--- a/docs/刘氏族谱资料/template.xlsx
+++ b/docs/刘氏族谱资料/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\liu_genealogy\frontend\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\liu_genealogy\docs\刘氏族谱资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCF7F15-516A-4D9C-826B-1D1DBA17D302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A915790-648C-481B-BEBC-1B3DB3277CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -660,6 +660,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T40"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="16.73046875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
